--- a/templates/CAPIT PREVI GM - template.xlsx
+++ b/templates/CAPIT PREVI GM - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$44</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="55" min="1" max="1"/>
@@ -1235,8 +1235,8 @@
     <col width="5.42578125" customWidth="1" style="55" min="8" max="8"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="55" min="9" max="9"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="55" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="55" min="11" max="18"/>
-    <col width="9.140625" customWidth="1" style="55" min="19" max="16384"/>
+    <col width="9.140625" customWidth="1" style="55" min="11" max="19"/>
+    <col width="9.140625" customWidth="1" style="55" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1402,111 +1402,111 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>1.51823482</v>
+        <v>1.54246162</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>-0.002608000042149339</v>
+        <v>0.001250669475249655</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F18" s="29" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>-4.805935025273589</v>
+        <v>2.304691771089579</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>1.52220473</v>
+        <v>1.54053492</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>-0.005084413312088643</v>
+        <v>0.001221228239944416</v>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F19" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G19" s="34" t="n">
-        <v>-9.36938635913369</v>
+        <v>2.25043844990322</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>1.5299838</v>
+        <v>1.53865587</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>-0.00142736048558989</v>
+        <v>0.005343685292252598</v>
       </c>
       <c r="E20" s="33" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F20" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>-2.6302920400778</v>
+        <v>9.84716407017816</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>1.53217076</v>
+        <v>1.53047748</v>
       </c>
       <c r="D21" s="33" t="n">
-        <v>0.00320394963733639</v>
+        <v>-0.001999187085239829</v>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F21" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G21" s="34" t="n">
-        <v>5.904130955687251</v>
+        <v>-3.684034923216669</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>1.52727744</v>
+        <v>1.53354332</v>
       </c>
       <c r="D22" s="33" t="n">
-        <v>-0.003548614595030863</v>
+        <v>0.0006642761460446955</v>
       </c>
       <c r="E22" s="33" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F22" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G22" s="34" t="n">
-        <v>-6.539267982296801</v>
+        <v>1.224105807183553</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1552,21 +1552,21 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="B25" s="35" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="36" t="inlineStr"/>
       <c r="D25" s="29" t="n">
-        <v>-0.01281333956001351</v>
+        <v>0.007819172578231504</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>0.01011461360166455</v>
+        <v>0.00328184861989711</v>
       </c>
       <c r="F25" s="29" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>-1.222254166129861</v>
+        <v>2.055066926026595</v>
       </c>
       <c r="H25" s="37" t="n"/>
     </row>
@@ -1578,16 +1578,16 @@
       </c>
       <c r="C26" s="40" t="inlineStr"/>
       <c r="D26" s="33" t="n">
-        <v>-0.01063111848011045</v>
+        <v>0.007211342501881601</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>0.01132875917954723</v>
+        <v>0.01295941951657587</v>
       </c>
       <c r="F26" s="33" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="G26" s="34" t="n">
-        <v>-0.916645226440389</v>
+        <v>0.6265055469393349</v>
       </c>
       <c r="H26" s="37" t="n"/>
     </row>
@@ -1599,16 +1599,16 @@
       </c>
       <c r="C27" s="40" t="inlineStr"/>
       <c r="D27" s="33" t="n">
-        <v>0.02313720299586719</v>
+        <v>0.03344721054803546</v>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0.03245009308684765</v>
+        <v>0.03663401720590143</v>
       </c>
       <c r="F27" s="33" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="G27" s="34" t="n">
-        <v>0.6556651742467047</v>
+        <v>0.9502411285507676</v>
       </c>
       <c r="H27" s="37" t="n"/>
     </row>
@@ -1620,16 +1620,16 @@
       </c>
       <c r="C28" s="40" t="inlineStr"/>
       <c r="D28" s="33" t="n">
-        <v>0.05235986460566155</v>
+        <v>0.06663376811974953</v>
       </c>
       <c r="E28" s="33" t="n">
-        <v>0.05658335107566681</v>
+        <v>0.06128941713981284</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>0.7285575389756034</v>
+        <v>0.9283674750258434</v>
       </c>
       <c r="H28" s="37" t="n"/>
     </row>
@@ -1642,260 +1642,282 @@
       </c>
       <c r="C29" s="40" t="inlineStr"/>
       <c r="D29" s="33" t="n">
-        <v>0.1339860592226958</v>
+        <v>0.1418809713486164</v>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.1101337668794067</v>
+        <v>0.11389765138259</v>
       </c>
       <c r="F29" s="33" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="G29" s="34" t="n">
-        <v>0.9064323454013677</v>
+        <v>0.9585513497794138</v>
       </c>
       <c r="H29" s="37" t="n"/>
     </row>
-    <row r="30" ht="15.95" customFormat="1" customHeight="1" s="21">
+    <row r="30" ht="15.95" customFormat="1" customHeight="1" s="38">
       <c r="A30" s="31" t="n"/>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr"/>
       <c r="D30" s="33" t="n">
-        <v>0.01774424073170944</v>
+        <v>0.1931015311041033</v>
       </c>
       <c r="E30" s="33" t="n">
-        <v>0.03025657239333235</v>
+        <v>0.2608130383273184</v>
       </c>
       <c r="F30" s="33" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>0.5470029012271665</v>
-      </c>
-      <c r="H30" s="53" t="n"/>
+        <v>0.6947835975396396</v>
+      </c>
+      <c r="H30" s="37" t="n"/>
     </row>
     <row r="31" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="A31" s="31" t="n"/>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C31" s="40" t="inlineStr"/>
       <c r="D31" s="33" t="n">
-        <v>0.1494590698907814</v>
+        <v>0.03398460476930887</v>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.1146833322510796</v>
+        <v>0.03884110435965238</v>
       </c>
       <c r="F31" s="33" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="G31" s="34" t="n">
-        <v>1.044198959948843</v>
+        <v>0.8930301301171285</v>
       </c>
       <c r="H31" s="53" t="n"/>
     </row>
-    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="38">
+    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="21">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="39" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr"/>
       <c r="D32" s="33" t="n">
-        <v>0.03868672659310968</v>
+        <v>0.1494590698907814</v>
       </c>
       <c r="E32" s="33" t="n">
-        <v>0.1263001749301305</v>
+        <v>0.1146833322510796</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>0.3542580710941606</v>
-      </c>
-      <c r="H32" s="37" t="n"/>
+        <v>1.044198959948843</v>
+      </c>
+      <c r="H32" s="53" t="n"/>
     </row>
     <row r="33" ht="15.95" customFormat="1" customHeight="1" s="38">
       <c r="A33" s="31" t="n"/>
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C33" s="40" t="inlineStr"/>
       <c r="D33" s="33" t="n">
-        <v>0.51823482</v>
+        <v>0.03868672659310968</v>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.6838725673202206</v>
+        <v>0.1263001749301305</v>
       </c>
       <c r="F33" s="33" t="n">
-        <v>0.7024186755536654</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="G33" s="34" t="n">
-        <v>0.7377862207201613</v>
+        <v>0.3542580710941606</v>
       </c>
       <c r="H33" s="37" t="n"/>
     </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="26.1" customHeight="1">
-      <c r="B35" s="54" t="inlineStr">
+    <row r="34" ht="15.95" customFormat="1" customHeight="1" s="38">
+      <c r="A34" s="31" t="n"/>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr"/>
+      <c r="D34" s="33" t="n">
+        <v>0.5424616200000001</v>
+      </c>
+      <c r="E34" s="33" t="n">
+        <v>0.6979033032249571</v>
+      </c>
+      <c r="F34" s="33" t="n">
+        <v>0.7116796535486569</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>0.7622272426858308</v>
+      </c>
+      <c r="H34" s="37" t="n"/>
+    </row>
+    <row r="35" ht="15.95" customHeight="1">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="26.1" customHeight="1">
+      <c r="B36" s="54" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="B36" s="41" t="inlineStr">
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="15.95" customHeight="1">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="25" t="n">
-        <v>86771120.14</v>
-      </c>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="15.95" customHeight="1">
-      <c r="B37" s="42" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C37" s="21" t="n"/>
       <c r="D37" s="21" t="n"/>
       <c r="E37" s="25" t="n">
-        <v>82362586.07031746</v>
+        <v>68026073.19</v>
       </c>
       <c r="F37" s="25" t="n"/>
       <c r="G37" s="25" t="n"/>
       <c r="H37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="41" t="n"/>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C38" s="21" t="n"/>
       <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="E38" s="25" t="n">
+        <v>82304967.81408729</v>
+      </c>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
       <c r="H38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="43" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
+      <c r="B39" s="41" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="n"/>
       <c r="H39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">² Cota Inicial em: </t>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C40" s="44" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
       <c r="H40" s="4" t="n"/>
     </row>
     <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="4" t="n"/>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="17" t="n"/>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">² Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
       <c r="H41" s="4" t="n"/>
     </row>
-    <row r="42" ht="40.5" customHeight="1">
+    <row r="42" ht="15.95" customHeight="1">
       <c r="A42" s="4" t="n"/>
-      <c r="B42" s="57" t="inlineStr">
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="17" t="n"/>
+      <c r="H42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="40.5" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="57" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="56" t="n"/>
       <c r="H43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
+      <c r="B44" s="56" t="n"/>
       <c r="H44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
       <c r="H45" s="4" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="4" t="n"/>
       <c r="B46" s="19" t="n"/>
       <c r="C46" s="20" t="n"/>
       <c r="D46" s="13" t="n"/>
       <c r="E46" s="13" t="n"/>
       <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
+      <c r="H46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B44:G44"/>
     <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B42:G42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>